--- a/data/Prohaska_EFH_liver_NIRpreds.xlsx
+++ b/data/Prohaska_EFH_liver_NIRpreds.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Esther.Goldstein\Work\Esther AG\Prohaska EFH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\fatmeter\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3EEA2DFA-9AA4-46C5-BC5D-41C75EA16EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585BE180-5F78-46E5-9F3D-64817B5756F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="1095" windowWidth="20025" windowHeight="14190" xr2:uid="{5DC1EC68-F235-43B5-94CF-791E92F7CEAC}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{5DC1EC68-F235-43B5-94CF-791E92F7CEAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Prohaska_EFH_liver_NIRpreds" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2249" uniqueCount="261">
   <si>
     <t>file_name</t>
   </si>
@@ -1305,13 +1305,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1702,7 +1699,8 @@
   <dimension ref="A1:AM148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="24" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="24" width="9.140625" customWidth="1"/>
     <col min="27" max="27" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10274,1074 +10272,1020 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>138</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73">
         <v>202101</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73">
         <v>148</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D73">
         <v>452346</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73">
         <v>21720</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" s="3" t="s">
+      <c r="H73" t="s">
         <v>139</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73">
         <v>139</v>
       </c>
-      <c r="J73" s="4">
+      <c r="J73" s="1">
         <v>44374</v>
       </c>
-      <c r="K73" s="3">
+      <c r="K73">
         <v>55.543039999999998</v>
       </c>
-      <c r="L73" s="3">
+      <c r="L73">
         <v>-155.66990000000001</v>
       </c>
-      <c r="M73" s="3">
+      <c r="M73">
         <v>0</v>
       </c>
-      <c r="N73" s="3">
+      <c r="N73">
         <v>6558270</v>
       </c>
-      <c r="O73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q73" s="3" t="s">
+      <c r="O73" t="s">
+        <v>41</v>
+      </c>
+      <c r="P73" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q73" t="s">
         <v>140</v>
       </c>
-      <c r="R73" s="3">
+      <c r="R73">
         <v>2021</v>
       </c>
-      <c r="S73" s="3">
+      <c r="S73">
         <v>2178</v>
       </c>
-      <c r="T73" s="3">
+      <c r="T73">
         <v>225689</v>
       </c>
-      <c r="U73" s="5">
+      <c r="U73" s="2">
         <v>45896.461805555555</v>
       </c>
-      <c r="V73" s="3" t="s">
+      <c r="V73" t="s">
         <v>43</v>
       </c>
-      <c r="W73" s="3" t="s">
+      <c r="W73" t="s">
         <v>141</v>
       </c>
-      <c r="X73" s="3" t="s">
+      <c r="X73" t="s">
         <v>142</v>
       </c>
-      <c r="Y73" s="3">
+      <c r="Y73">
         <v>3</v>
       </c>
-      <c r="Z73" s="3" t="s">
+      <c r="Z73" t="s">
         <v>46</v>
       </c>
-      <c r="AA73" s="3" t="s">
+      <c r="AA73" t="s">
         <v>143</v>
       </c>
-      <c r="AB73" s="4">
+      <c r="AB73" s="1">
         <v>44374</v>
       </c>
-      <c r="AC73" s="3">
+      <c r="AC73">
         <v>55.543039999999998</v>
       </c>
-      <c r="AD73" s="3">
+      <c r="AD73">
         <v>-155.66990000000001</v>
       </c>
-      <c r="AE73" s="3">
+      <c r="AE73">
         <v>139</v>
       </c>
-      <c r="AF73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG73" s="3">
+      <c r="AF73" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG73">
         <v>55.367730000000002</v>
       </c>
-      <c r="AH73" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI73" s="3">
+      <c r="AH73" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI73">
         <v>39.374393027674699</v>
       </c>
-      <c r="AJ73" s="3">
+      <c r="AJ73">
         <v>39.113757880977097</v>
       </c>
-      <c r="AK73" s="3" t="s">
+      <c r="AK73" t="s">
         <v>144</v>
       </c>
-      <c r="AL73" s="3" t="s">
+      <c r="AL73" t="s">
         <v>49</v>
       </c>
-      <c r="AM73" s="3" t="s">
+      <c r="AM73" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74">
         <v>202101</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74">
         <v>148</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D74">
         <v>452347</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74">
         <v>21720</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H74" s="3" t="s">
+      <c r="H74" t="s">
         <v>139</v>
       </c>
-      <c r="I74" s="3">
+      <c r="I74">
         <v>139</v>
       </c>
-      <c r="J74" s="4">
+      <c r="J74" s="1">
         <v>44374</v>
       </c>
-      <c r="K74" s="3">
+      <c r="K74">
         <v>55.543039999999998</v>
       </c>
-      <c r="L74" s="3">
+      <c r="L74">
         <v>-155.66990000000001</v>
       </c>
-      <c r="M74" s="3">
+      <c r="M74">
         <v>0</v>
       </c>
-      <c r="N74" s="3">
+      <c r="N74">
         <v>6558271</v>
       </c>
-      <c r="O74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q74" s="3" t="s">
+      <c r="O74" t="s">
+        <v>41</v>
+      </c>
+      <c r="P74" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q74" t="s">
         <v>140</v>
       </c>
-      <c r="R74" s="3">
+      <c r="R74">
         <v>2021</v>
       </c>
-      <c r="S74" s="3">
+      <c r="S74">
         <v>2178</v>
       </c>
-      <c r="T74" s="3">
+      <c r="T74">
         <v>225766</v>
       </c>
-      <c r="U74" s="5">
+      <c r="U74" s="2">
         <v>45896.487500000003</v>
       </c>
-      <c r="V74" s="3" t="s">
+      <c r="V74" t="s">
         <v>43</v>
       </c>
-      <c r="W74" s="3" t="s">
+      <c r="W74" t="s">
         <v>141</v>
       </c>
-      <c r="X74" s="3" t="s">
+      <c r="X74" t="s">
         <v>142</v>
       </c>
-      <c r="Y74" s="3">
+      <c r="Y74">
         <v>4</v>
       </c>
-      <c r="Z74" s="3" t="s">
+      <c r="Z74" t="s">
         <v>46</v>
       </c>
-      <c r="AA74" s="3" t="s">
+      <c r="AA74" t="s">
         <v>143</v>
       </c>
-      <c r="AB74" s="4">
+      <c r="AB74" s="1">
         <v>44374</v>
       </c>
-      <c r="AC74" s="3">
+      <c r="AC74">
         <v>55.543039999999998</v>
       </c>
-      <c r="AD74" s="3">
+      <c r="AD74">
         <v>-155.66990000000001</v>
       </c>
-      <c r="AE74" s="3">
+      <c r="AE74">
         <v>139</v>
       </c>
-      <c r="AF74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG74" s="3">
+      <c r="AF74" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG74">
         <v>54.230780000000003</v>
       </c>
-      <c r="AH74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI74" s="3">
+      <c r="AH74" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI74">
         <v>47.067039538950198</v>
       </c>
-      <c r="AJ74" s="3">
+      <c r="AJ74">
         <v>46.951111684262798</v>
       </c>
-      <c r="AK74" s="3" t="s">
+      <c r="AK74" t="s">
         <v>144</v>
       </c>
-      <c r="AL74" s="3" t="s">
+      <c r="AL74" t="s">
         <v>49</v>
       </c>
-      <c r="AM74" s="3" t="s">
+      <c r="AM74" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>146</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75">
         <v>202101</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75">
         <v>148</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D75">
         <v>452360</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75">
         <v>21720</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H75" s="3" t="s">
+      <c r="H75" t="s">
         <v>139</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I75">
         <v>156</v>
       </c>
-      <c r="J75" s="4">
+      <c r="J75" s="1">
         <v>44377</v>
       </c>
-      <c r="K75" s="3">
+      <c r="K75">
         <v>57.185209999999998</v>
       </c>
-      <c r="L75" s="3">
+      <c r="L75">
         <v>-151.43340000000001</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M75">
         <v>0</v>
       </c>
-      <c r="N75" s="3">
+      <c r="N75">
         <v>6558288</v>
       </c>
-      <c r="O75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q75" s="3" t="s">
+      <c r="O75" t="s">
+        <v>41</v>
+      </c>
+      <c r="P75" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q75" t="s">
         <v>140</v>
       </c>
-      <c r="R75" s="3">
+      <c r="R75">
         <v>2021</v>
       </c>
-      <c r="S75" s="3">
+      <c r="S75">
         <v>2178</v>
       </c>
-      <c r="T75" s="3">
+      <c r="T75">
         <v>225711</v>
       </c>
-      <c r="U75" s="5">
+      <c r="U75" s="2">
         <v>45890.668749999997</v>
       </c>
-      <c r="V75" s="3" t="s">
+      <c r="V75" t="s">
         <v>43</v>
       </c>
-      <c r="W75" s="3" t="s">
+      <c r="W75" t="s">
         <v>141</v>
       </c>
-      <c r="X75" s="3" t="s">
+      <c r="X75" t="s">
         <v>142</v>
       </c>
-      <c r="Y75" s="3">
+      <c r="Y75">
         <v>3</v>
       </c>
-      <c r="Z75" s="3" t="s">
+      <c r="Z75" t="s">
         <v>46</v>
       </c>
-      <c r="AA75" s="3" t="s">
+      <c r="AA75" t="s">
         <v>147</v>
       </c>
-      <c r="AB75" s="4">
+      <c r="AB75" s="1">
         <v>44377</v>
       </c>
-      <c r="AC75" s="3">
+      <c r="AC75">
         <v>57.185209999999998</v>
       </c>
-      <c r="AD75" s="3">
+      <c r="AD75">
         <v>-151.43340000000001</v>
       </c>
-      <c r="AE75" s="3">
+      <c r="AE75">
         <v>156</v>
       </c>
-      <c r="AF75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG75" s="3">
+      <c r="AF75" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG75">
         <v>46.542720000000003</v>
       </c>
-      <c r="AH75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI75" s="3">
+      <c r="AH75" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI75">
         <v>48.541086612749602</v>
       </c>
-      <c r="AJ75" s="3">
+      <c r="AJ75">
         <v>48.567806981965099</v>
       </c>
-      <c r="AK75" s="3" t="s">
+      <c r="AK75" t="s">
         <v>144</v>
       </c>
-      <c r="AL75" s="3" t="s">
+      <c r="AL75" t="s">
         <v>49</v>
       </c>
-      <c r="AM75" s="3" t="s">
+      <c r="AM75" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>148</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76">
         <v>202101</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76">
         <v>148</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76">
         <v>452361</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76">
         <v>21720</v>
       </c>
-      <c r="F76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" t="s">
         <v>139</v>
       </c>
-      <c r="I76" s="3">
+      <c r="I76">
         <v>171</v>
       </c>
-      <c r="J76" s="4">
+      <c r="J76" s="1">
         <v>44381</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76">
         <v>58.200389999999999</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76">
         <v>-151.24109999999999</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76">
         <v>0</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76">
         <v>6558302</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q76" s="3" t="s">
+      <c r="O76" t="s">
+        <v>41</v>
+      </c>
+      <c r="P76" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q76" t="s">
         <v>140</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76">
         <v>2021</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76">
         <v>2178</v>
       </c>
-      <c r="T76" s="3">
+      <c r="T76">
         <v>225700</v>
       </c>
-      <c r="U76" s="5">
+      <c r="U76" s="2">
         <v>45890.670138888891</v>
       </c>
-      <c r="V76" s="3" t="s">
+      <c r="V76" t="s">
         <v>43</v>
       </c>
-      <c r="W76" s="3" t="s">
+      <c r="W76" t="s">
         <v>141</v>
       </c>
-      <c r="X76" s="3" t="s">
+      <c r="X76" t="s">
         <v>142</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Y76">
         <v>1</v>
       </c>
-      <c r="Z76" s="3" t="s">
+      <c r="Z76" t="s">
         <v>46</v>
       </c>
-      <c r="AA76" s="3" t="s">
+      <c r="AA76" t="s">
         <v>149</v>
       </c>
-      <c r="AB76" s="4">
+      <c r="AB76" s="1">
         <v>44381</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AC76">
         <v>58.200389999999999</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AD76">
         <v>-151.24109999999999</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AE76">
         <v>171</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AF76" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG76">
         <v>48.431069999999998</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AH76" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI76">
         <v>58.951199097523101</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AJ76">
         <v>59.315555052507598</v>
       </c>
-      <c r="AK76" s="3" t="s">
+      <c r="AK76" t="s">
         <v>144</v>
       </c>
-      <c r="AL76" s="3" t="s">
+      <c r="AL76" t="s">
         <v>49</v>
       </c>
-      <c r="AM76" s="3" t="s">
+      <c r="AM76" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>150</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77">
         <v>202101</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77">
         <v>148</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D77">
         <v>452362</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77">
         <v>21720</v>
       </c>
-      <c r="F77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H77" s="3" t="s">
+      <c r="H77" t="s">
         <v>139</v>
       </c>
-      <c r="I77" s="3">
+      <c r="I77">
         <v>171</v>
       </c>
-      <c r="J77" s="4">
+      <c r="J77" s="1">
         <v>44381</v>
       </c>
-      <c r="K77" s="3">
+      <c r="K77">
         <v>58.200389999999999</v>
       </c>
-      <c r="L77" s="3">
+      <c r="L77">
         <v>-151.24109999999999</v>
       </c>
-      <c r="M77" s="3">
+      <c r="M77">
         <v>0</v>
       </c>
-      <c r="N77" s="3">
+      <c r="N77">
         <v>6558303</v>
       </c>
-      <c r="O77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q77" s="3" t="s">
+      <c r="O77" t="s">
+        <v>41</v>
+      </c>
+      <c r="P77" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q77" t="s">
         <v>140</v>
       </c>
-      <c r="R77" s="3">
+      <c r="R77">
         <v>2021</v>
       </c>
-      <c r="S77" s="3">
+      <c r="S77">
         <v>2178</v>
       </c>
-      <c r="T77" s="3">
+      <c r="T77">
         <v>225723</v>
       </c>
-      <c r="U77" s="5">
+      <c r="U77" s="2">
         <v>45890.615972222222</v>
       </c>
-      <c r="V77" s="3" t="s">
+      <c r="V77" t="s">
         <v>43</v>
       </c>
-      <c r="W77" s="3" t="s">
+      <c r="W77" t="s">
         <v>141</v>
       </c>
-      <c r="X77" s="3" t="s">
+      <c r="X77" t="s">
         <v>142</v>
       </c>
-      <c r="Y77" s="3">
+      <c r="Y77">
         <v>2</v>
       </c>
-      <c r="Z77" s="3" t="s">
+      <c r="Z77" t="s">
         <v>46</v>
       </c>
-      <c r="AA77" s="3" t="s">
+      <c r="AA77" t="s">
         <v>149</v>
       </c>
-      <c r="AB77" s="4">
+      <c r="AB77" s="1">
         <v>44381</v>
       </c>
-      <c r="AC77" s="3">
+      <c r="AC77">
         <v>58.200389999999999</v>
       </c>
-      <c r="AD77" s="3">
+      <c r="AD77">
         <v>-151.24109999999999</v>
       </c>
-      <c r="AE77" s="3">
+      <c r="AE77">
         <v>171</v>
       </c>
-      <c r="AF77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG77" s="3">
+      <c r="AF77" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG77">
         <v>43.750500000000002</v>
       </c>
-      <c r="AH77" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI77" s="3">
+      <c r="AH77" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI77">
         <v>57.7225179515126</v>
       </c>
-      <c r="AJ77" s="3">
+      <c r="AJ77">
         <v>58.163773366043898</v>
       </c>
-      <c r="AK77" s="3" t="s">
+      <c r="AK77" t="s">
         <v>144</v>
       </c>
-      <c r="AL77" s="3" t="s">
+      <c r="AL77" t="s">
         <v>49</v>
       </c>
-      <c r="AM77" s="3" t="s">
+      <c r="AM77" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>151</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78">
         <v>202101</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78">
         <v>148</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D78">
         <v>452371</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E78">
         <v>21720</v>
       </c>
-      <c r="F78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" t="s">
         <v>139</v>
       </c>
-      <c r="I78" s="3">
+      <c r="I78">
         <v>187</v>
       </c>
-      <c r="J78" s="4">
+      <c r="J78" s="1">
         <v>44384</v>
       </c>
-      <c r="K78" s="3">
+      <c r="K78">
         <v>58.507669999999997</v>
       </c>
-      <c r="L78" s="3">
+      <c r="L78">
         <v>-149.20009999999999</v>
       </c>
-      <c r="M78" s="3">
+      <c r="M78">
         <v>0</v>
       </c>
-      <c r="N78" s="3">
+      <c r="N78">
         <v>6558307</v>
       </c>
-      <c r="O78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q78" s="3" t="s">
+      <c r="O78" t="s">
+        <v>41</v>
+      </c>
+      <c r="P78" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q78" t="s">
         <v>140</v>
       </c>
-      <c r="R78" s="3">
+      <c r="R78">
         <v>2021</v>
       </c>
-      <c r="S78" s="3">
+      <c r="S78">
         <v>2178</v>
       </c>
-      <c r="T78" s="3">
+      <c r="T78">
         <v>225734</v>
       </c>
-      <c r="U78" s="5">
+      <c r="U78" s="2">
         <v>45890.635416666664</v>
       </c>
-      <c r="V78" s="3" t="s">
+      <c r="V78" t="s">
         <v>43</v>
       </c>
-      <c r="W78" s="3" t="s">
+      <c r="W78" t="s">
         <v>141</v>
       </c>
-      <c r="X78" s="3" t="s">
+      <c r="X78" t="s">
         <v>142</v>
       </c>
-      <c r="Y78" s="3">
+      <c r="Y78">
         <v>2</v>
       </c>
-      <c r="Z78" s="3" t="s">
+      <c r="Z78" t="s">
         <v>46</v>
       </c>
-      <c r="AA78" s="3" t="s">
+      <c r="AA78" t="s">
         <v>152</v>
       </c>
-      <c r="AB78" s="4">
+      <c r="AB78" s="1">
         <v>44384</v>
       </c>
-      <c r="AC78" s="3">
+      <c r="AC78">
         <v>58.507669999999997</v>
       </c>
-      <c r="AD78" s="3">
+      <c r="AD78">
         <v>-149.20009999999999</v>
       </c>
-      <c r="AE78" s="3">
+      <c r="AE78">
         <v>187</v>
       </c>
-      <c r="AF78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG78" s="3">
+      <c r="AF78" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG78">
         <v>53.315089999999998</v>
       </c>
-      <c r="AH78" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI78" s="3">
+      <c r="AH78" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI78">
         <v>61.192192538206399</v>
       </c>
-      <c r="AJ78" s="3">
+      <c r="AJ78">
         <v>61.478542444403402</v>
       </c>
-      <c r="AK78" s="3" t="s">
+      <c r="AK78" t="s">
         <v>144</v>
       </c>
-      <c r="AL78" s="3" t="s">
+      <c r="AL78" t="s">
         <v>49</v>
       </c>
-      <c r="AM78" s="3" t="s">
+      <c r="AM78" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>153</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79">
         <v>202101</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79">
         <v>148</v>
       </c>
-      <c r="D79" s="3">
+      <c r="D79">
         <v>452372</v>
       </c>
-      <c r="E79" s="3">
+      <c r="E79">
         <v>21720</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H79" s="3" t="s">
+      <c r="H79" t="s">
         <v>139</v>
       </c>
-      <c r="I79" s="3">
+      <c r="I79">
         <v>187</v>
       </c>
-      <c r="J79" s="4">
+      <c r="J79" s="1">
         <v>44384</v>
       </c>
-      <c r="K79" s="3">
+      <c r="K79">
         <v>58.507669999999997</v>
       </c>
-      <c r="L79" s="3">
+      <c r="L79">
         <v>-149.20009999999999</v>
       </c>
-      <c r="M79" s="3">
+      <c r="M79">
         <v>0</v>
       </c>
-      <c r="N79" s="3">
+      <c r="N79">
         <v>6558308</v>
       </c>
-      <c r="O79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q79" s="3" t="s">
+      <c r="O79" t="s">
+        <v>41</v>
+      </c>
+      <c r="P79" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q79" t="s">
         <v>140</v>
       </c>
-      <c r="R79" s="3">
+      <c r="R79">
         <v>2021</v>
       </c>
-      <c r="S79" s="3">
+      <c r="S79">
         <v>2178</v>
       </c>
-      <c r="T79" s="3">
+      <c r="T79">
         <v>225745</v>
       </c>
-      <c r="U79" s="5">
+      <c r="U79" s="2">
         <v>45896.459027777775</v>
       </c>
-      <c r="V79" s="3" t="s">
+      <c r="V79" t="s">
         <v>43</v>
       </c>
-      <c r="W79" s="3" t="s">
+      <c r="W79" t="s">
         <v>141</v>
       </c>
-      <c r="X79" s="3" t="s">
+      <c r="X79" t="s">
         <v>142</v>
       </c>
-      <c r="Y79" s="3">
+      <c r="Y79">
         <v>3</v>
       </c>
-      <c r="Z79" s="3" t="s">
+      <c r="Z79" t="s">
         <v>46</v>
       </c>
-      <c r="AA79" s="3" t="s">
+      <c r="AA79" t="s">
         <v>152</v>
       </c>
-      <c r="AB79" s="4">
+      <c r="AB79" s="1">
         <v>44384</v>
       </c>
-      <c r="AC79" s="3">
+      <c r="AC79">
         <v>58.507669999999997</v>
       </c>
-      <c r="AD79" s="3">
+      <c r="AD79">
         <v>-149.20009999999999</v>
       </c>
-      <c r="AE79" s="3">
+      <c r="AE79">
         <v>187</v>
       </c>
-      <c r="AF79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG79" s="3">
+      <c r="AF79" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG79">
         <v>48.199469999999998</v>
       </c>
-      <c r="AH79" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI79" s="3">
+      <c r="AH79" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI79">
         <v>52.249294641221901</v>
       </c>
-      <c r="AJ79" s="3">
+      <c r="AJ79">
         <v>52.314979559224298</v>
       </c>
-      <c r="AK79" s="3" t="s">
+      <c r="AK79" t="s">
         <v>144</v>
       </c>
-      <c r="AL79" s="3" t="s">
+      <c r="AL79" t="s">
         <v>49</v>
       </c>
-      <c r="AM79" s="3" t="s">
+      <c r="AM79" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>154</v>
       </c>
-      <c r="B80" s="3">
+      <c r="B80">
         <v>202101</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80">
         <v>148</v>
       </c>
-      <c r="D80" s="3">
+      <c r="D80">
         <v>452374</v>
       </c>
-      <c r="E80" s="3">
+      <c r="E80">
         <v>21720</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H80" s="3" t="s">
+      <c r="H80" t="s">
         <v>139</v>
       </c>
-      <c r="I80" s="3">
+      <c r="I80">
         <v>187</v>
       </c>
-      <c r="J80" s="4">
+      <c r="J80" s="1">
         <v>44384</v>
       </c>
-      <c r="K80" s="3">
+      <c r="K80">
         <v>58.507669999999997</v>
       </c>
-      <c r="L80" s="3">
+      <c r="L80">
         <v>-149.20009999999999</v>
       </c>
-      <c r="M80" s="3">
+      <c r="M80">
         <v>0</v>
       </c>
-      <c r="N80" s="3">
+      <c r="N80">
         <v>6558310</v>
       </c>
-      <c r="O80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q80" s="3" t="s">
+      <c r="O80" t="s">
+        <v>41</v>
+      </c>
+      <c r="P80" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q80" t="s">
         <v>140</v>
       </c>
-      <c r="R80" s="3">
+      <c r="R80">
         <v>2021</v>
       </c>
-      <c r="S80" s="3">
+      <c r="S80">
         <v>2178</v>
       </c>
-      <c r="T80" s="3">
+      <c r="T80">
         <v>225701</v>
       </c>
-      <c r="U80" s="5">
+      <c r="U80" s="2">
         <v>45890.612500000003</v>
       </c>
-      <c r="V80" s="3" t="s">
+      <c r="V80" t="s">
         <v>43</v>
       </c>
-      <c r="W80" s="3" t="s">
+      <c r="W80" t="s">
         <v>141</v>
       </c>
-      <c r="X80" s="3" t="s">
+      <c r="X80" t="s">
         <v>142</v>
       </c>
-      <c r="Y80" s="3">
+      <c r="Y80">
         <v>5</v>
       </c>
-      <c r="Z80" s="3" t="s">
+      <c r="Z80" t="s">
         <v>46</v>
       </c>
-      <c r="AA80" s="3" t="s">
+      <c r="AA80" t="s">
         <v>152</v>
       </c>
-      <c r="AB80" s="4">
+      <c r="AB80" s="1">
         <v>44384</v>
       </c>
-      <c r="AC80" s="3">
+      <c r="AC80">
         <v>58.507669999999997</v>
       </c>
-      <c r="AD80" s="3">
+      <c r="AD80">
         <v>-149.20009999999999</v>
       </c>
-      <c r="AE80" s="3">
+      <c r="AE80">
         <v>187</v>
       </c>
-      <c r="AF80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG80" s="3">
+      <c r="AF80" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG80">
         <v>64.742350000000002</v>
       </c>
-      <c r="AH80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI80" s="3">
+      <c r="AH80" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI80">
         <v>62.010571219438297</v>
       </c>
-      <c r="AJ80" s="3">
+      <c r="AJ80">
         <v>61.750358603963697</v>
       </c>
-      <c r="AK80" s="3" t="s">
+      <c r="AK80" t="s">
         <v>144</v>
       </c>
-      <c r="AL80" s="3" t="s">
+      <c r="AL80" t="s">
         <v>49</v>
       </c>
-      <c r="AM80" s="3" t="s">
+      <c r="AM80" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:39" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>155</v>
       </c>
-      <c r="B81" s="3">
+      <c r="B81">
         <v>202101</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81">
         <v>148</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81">
         <v>452375</v>
       </c>
-      <c r="E81" s="3">
+      <c r="E81">
         <v>21720</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" t="s">
         <v>139</v>
       </c>
-      <c r="I81" s="3">
+      <c r="I81">
         <v>187</v>
       </c>
-      <c r="J81" s="4">
+      <c r="J81" s="1">
         <v>44384</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81">
         <v>58.507669999999997</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81">
         <v>-149.20009999999999</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81">
         <v>0</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81">
         <v>6558311</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q81" s="3" t="s">
+      <c r="O81" t="s">
+        <v>41</v>
+      </c>
+      <c r="P81" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q81" t="s">
         <v>140</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81">
         <v>2021</v>
       </c>
-      <c r="S81" s="3">
+      <c r="S81">
         <v>2178</v>
       </c>
-      <c r="T81" s="3">
+      <c r="T81">
         <v>225724</v>
       </c>
-      <c r="U81" s="5">
+      <c r="U81" s="2">
         <v>45890.666666666664</v>
       </c>
-      <c r="V81" s="3" t="s">
+      <c r="V81" t="s">
         <v>43</v>
       </c>
-      <c r="W81" s="3" t="s">
+      <c r="W81" t="s">
         <v>141</v>
       </c>
-      <c r="X81" s="3" t="s">
+      <c r="X81" t="s">
         <v>142</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Y81">
         <v>6</v>
       </c>
-      <c r="Z81" s="3" t="s">
+      <c r="Z81" t="s">
         <v>46</v>
       </c>
-      <c r="AA81" s="3" t="s">
+      <c r="AA81" t="s">
         <v>152</v>
       </c>
-      <c r="AB81" s="4">
+      <c r="AB81" s="1">
         <v>44384</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AC81">
         <v>58.507669999999997</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AD81">
         <v>-149.20009999999999</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AE81">
         <v>187</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AF81" t="s">
+        <v>41</v>
+      </c>
+      <c r="AG81">
         <v>57.587589999999999</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AH81" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI81">
         <v>61.306164302874699</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AJ81">
         <v>61.390601896188002</v>
       </c>
-      <c r="AK81" s="3" t="s">
+      <c r="AK81" t="s">
         <v>144</v>
       </c>
-      <c r="AL81" s="3" t="s">
+      <c r="AL81" t="s">
         <v>49</v>
       </c>
-      <c r="AM81" s="3" t="s">
+      <c r="AM81" t="s">
         <v>50</v>
       </c>
     </row>
@@ -11361,11 +11305,11 @@
       <c r="E82">
         <v>21720</v>
       </c>
-      <c r="F82" t="s">
-        <v>41</v>
-      </c>
-      <c r="G82" t="s">
-        <v>41</v>
+      <c r="F82">
+        <v>550</v>
+      </c>
+      <c r="G82">
+        <v>1820</v>
       </c>
       <c r="H82" t="s">
         <v>40</v>
@@ -11480,11 +11424,11 @@
       <c r="E83">
         <v>21720</v>
       </c>
-      <c r="F83" t="s">
-        <v>41</v>
-      </c>
-      <c r="G83" t="s">
-        <v>41</v>
+      <c r="F83">
+        <v>590</v>
+      </c>
+      <c r="G83">
+        <v>2240</v>
       </c>
       <c r="H83" t="s">
         <v>40</v>
@@ -11602,8 +11546,8 @@
       <c r="F84">
         <v>440</v>
       </c>
-      <c r="G84" t="s">
-        <v>41</v>
+      <c r="G84">
+        <v>925</v>
       </c>
       <c r="H84" t="s">
         <v>40</v>
@@ -11722,7 +11666,7 @@
         <v>460</v>
       </c>
       <c r="G85">
-        <v>95</v>
+        <v>995</v>
       </c>
       <c r="H85" t="s">
         <v>40</v>
@@ -12552,7 +12496,7 @@
         <v>21720</v>
       </c>
       <c r="F92">
-        <v>51</v>
+        <v>510</v>
       </c>
       <c r="G92">
         <v>1565</v>
@@ -12671,7 +12615,7 @@
         <v>21720</v>
       </c>
       <c r="F93">
-        <v>82</v>
+        <v>820</v>
       </c>
       <c r="G93">
         <v>6675</v>
@@ -12790,7 +12734,7 @@
         <v>21720</v>
       </c>
       <c r="F94">
-        <v>94</v>
+        <v>940</v>
       </c>
       <c r="G94">
         <v>10815</v>
@@ -12909,7 +12853,7 @@
         <v>21720</v>
       </c>
       <c r="F95">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="G95">
         <v>9995</v>
@@ -13031,7 +12975,7 @@
         <v>780</v>
       </c>
       <c r="G96">
-        <v>6515</v>
+        <v>6215</v>
       </c>
       <c r="H96" t="s">
         <v>40</v>
@@ -13504,7 +13448,7 @@
         <v>21720</v>
       </c>
       <c r="F100">
-        <v>66</v>
+        <v>660</v>
       </c>
       <c r="G100">
         <v>3715</v>
@@ -13623,7 +13567,7 @@
         <v>21720</v>
       </c>
       <c r="F101">
-        <v>69</v>
+        <v>690</v>
       </c>
       <c r="G101">
         <v>4060</v>
@@ -13742,7 +13686,7 @@
         <v>21720</v>
       </c>
       <c r="F102">
-        <v>87</v>
+        <v>870</v>
       </c>
       <c r="G102">
         <v>8665</v>
@@ -14098,11 +14042,11 @@
       <c r="E105">
         <v>21720</v>
       </c>
-      <c r="F105" t="s">
-        <v>41</v>
-      </c>
-      <c r="G105" t="s">
-        <v>41</v>
+      <c r="F105">
+        <v>720</v>
+      </c>
+      <c r="G105">
+        <v>4642</v>
       </c>
       <c r="H105" t="s">
         <v>40</v>
@@ -15054,7 +14998,7 @@
         <v>640</v>
       </c>
       <c r="G113">
-        <v>5520</v>
+        <v>3010</v>
       </c>
       <c r="H113" t="s">
         <v>40</v>
@@ -15292,7 +15236,7 @@
         <v>810</v>
       </c>
       <c r="G115">
-        <v>3010</v>
+        <v>5520</v>
       </c>
       <c r="H115" t="s">
         <v>40</v>
@@ -16482,7 +16426,7 @@
         <v>690</v>
       </c>
       <c r="G125">
-        <v>3898</v>
+        <v>3895</v>
       </c>
       <c r="H125" t="s">
         <v>40</v>
@@ -19334,53 +19278,53 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
+      <c r="A3" s="3"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="5" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
+      <c r="A9" s="3"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="5" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="5" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="6" t="s">
         <v>258</v>
       </c>
     </row>
@@ -19390,53 +19334,53 @@
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="4" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
+      <c r="A17" s="3"/>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="5" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
+      <c r="A23" s="3"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="5" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="5" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="6" t="s">
         <v>254</v>
       </c>
     </row>
